--- a/inst/extdata/mocaredd-template-v2-4pools.xlsx
+++ b/inst/extdata/mocaredd-template-v2-4pools.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaelsola/code/mocaredd.dev2/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCFB189-B6D3-4E4D-9590-1A26B4BB0554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92C6505-163F-604F-8AD7-804EF7233CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="760" windowWidth="28660" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33140" yWindow="-3540" windowWidth="28660" windowHeight="18460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="user" sheetId="5" r:id="rId1"/>
+    <sheet name="setup" sheetId="5" r:id="rId1"/>
     <sheet name="time" sheetId="4" r:id="rId2"/>
     <sheet name="area" sheetId="10" r:id="rId3"/>
     <sheet name="carbon" sheetId="9" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
